--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92569710284</v>
+        <v>46157.93103910026</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93103910026</v>
+        <v>46157.93175360985</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93175360985</v>
+        <v>46157.93401294846</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93401294846</v>
+        <v>46157.93719267685</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93719267685</v>
+        <v>46158.2821745936</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2821745936</v>
+        <v>46158.29683226448</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29683226448</v>
+        <v>46158.29816146589</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29816146589</v>
+        <v>46158.33388490351</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388490351</v>
+        <v>46158.36858304378</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36858304378</v>
+        <v>46158.37288976945</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
